--- a/Last-Bite-Backend/docs/Database.xlsx
+++ b/Last-Bite-Backend/docs/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidsantiago/Desktop/BackendMoviles/MOBILE_APP_DEV_BACKEND-S4-G4/Last-Bite-Backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A97037-E2AA-9740-A2F6-DCE08AEE5BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139B2835-2AC2-B345-AAAB-43D411BA2CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15620" xr2:uid="{47F1251A-4F32-B949-8330-818A2A4EE1EB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="56">
   <si>
     <t>USER</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>UNIT_PRICE</t>
+  </si>
+  <si>
+    <t>SCORE</t>
+  </si>
+  <si>
+    <t>NULL</t>
   </si>
 </sst>
 </file>
@@ -349,6 +355,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -361,11 +372,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -713,7 +719,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -730,7 +736,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -745,7 +751,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -760,7 +766,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -775,7 +781,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -790,248 +796,248 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="11">
-        <v>1</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="7">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="11">
+      <c r="A11" s="13"/>
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="11">
+      <c r="A12" s="13"/>
+      <c r="B12" s="7">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="13"/>
+      <c r="B15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-      <c r="B16" s="11">
-        <v>1</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="7">
+        <v>1</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="11">
-        <v>1</v>
-      </c>
-      <c r="F16" s="12" t="s">
+      <c r="E16" s="7">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="7">
         <v>12000</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="7">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="11">
+      <c r="A17" s="13"/>
+      <c r="B17" s="7">
         <v>2</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="11">
-        <v>1</v>
-      </c>
-      <c r="F17" s="12" t="s">
+      <c r="E17" s="7">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="7">
         <v>13000</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="11">
+      <c r="A18" s="13"/>
+      <c r="B18" s="7">
         <v>3</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="11">
-        <v>1</v>
-      </c>
-      <c r="F18" s="12" t="s">
+      <c r="E18" s="7">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="7">
         <v>5000</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="7">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="C20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="10" t="s">
+      <c r="A21" s="13"/>
+      <c r="B21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="11">
+      <c r="A22" s="13"/>
+      <c r="B22" s="7">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1042,8 +1048,8 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="11">
+      <c r="A23" s="13"/>
+      <c r="B23" s="7">
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1054,8 +1060,8 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="11">
+      <c r="A24" s="13"/>
+      <c r="B24" s="7">
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -1066,167 +1072,182 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
-      <c r="B27" s="10" t="s">
+      <c r="A27" s="13"/>
+      <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
-      <c r="B28" s="11">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13">
+      <c r="A28" s="13"/>
+      <c r="B28" s="7">
+        <v>1</v>
+      </c>
+      <c r="C28" s="9">
         <v>45658</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="7">
         <v>120000</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="11">
+      <c r="A29" s="13"/>
+      <c r="B29" s="7">
         <v>2</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="9">
         <v>45659</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="7">
         <v>13000</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
-      <c r="B30" s="11">
+      <c r="A30" s="13"/>
+      <c r="B30" s="7">
         <v>3</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="9">
         <v>45660</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="7">
         <v>5000</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
-      <c r="B33" s="10" t="s">
+      <c r="E32" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="13"/>
+      <c r="B33" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="8"/>
-      <c r="B34" s="11">
-        <v>1</v>
-      </c>
-      <c r="C34" s="11">
-        <v>1</v>
-      </c>
-      <c r="D34" s="11">
+      <c r="E33" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="13"/>
+      <c r="B34" s="7">
+        <v>1</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="11">
+      <c r="E34" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="13"/>
+      <c r="B35" s="7">
         <v>2</v>
       </c>
-      <c r="C35" s="11">
-        <v>1</v>
-      </c>
-      <c r="D35" s="11">
+      <c r="C35" s="7">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
-      <c r="B36" s="11">
+      <c r="E35" s="7">
         <v>3</v>
       </c>
-      <c r="C36" s="11">
-        <v>1</v>
-      </c>
-      <c r="D36" s="11">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="13"/>
+      <c r="B36" s="7">
+        <v>3</v>
+      </c>
+      <c r="C36" s="7">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7">
         <v>4</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A32:A36"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A20:A24"/>
     <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A32:A36"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
